--- a/astro-site/public/dl/haccp-templates/03-cleaning-sanitizing-schedule.xlsx
+++ b/astro-site/public/dl/haccp-templates/03-cleaning-sanitizing-schedule.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>Food-grade degreaser + food-contact surface sanitizer</t>
+          <t>Food-contact sanitizer at label concentration (chlorine 50-200 ppm, quat per label), checked with test strips (§4-501.114, §4-302.14)</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Remove debris, spray, let it work for the stated time, rinse and dry with single-use paper towels</t>
+          <t>Remove debris, wash with the degreaser and rinse, then spray the sanitizer, leave it for the stated contact time and let it air-dry. Each service and every 4 h while in continuous use with TCS food (§4-602.11)</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>Acid descaler (rinse completely) — sanitize in a SECOND pass with bleach (sodium hypochlorite) 1:50</t>
+          <t>Acid descaler (rinse completely) — sanitize in a SECOND pass with chlorine 50-200 ppm (about 1 tsp of regular bleach per gallon), verify with test strips</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Dishwasher: final sanitizing rinse at 180 °F (165 °F in a stationary-rack, single-temperature machine; §4-501.112)</t>
+          <t>Dishwasher: final sanitizing rinse at 180 °F (165 °F in a stationary-rack, single-temperature machine; §4-501.112); low-temperature chemical machine: 50-100 ppm chlorine at the final rinse</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Trash cans, restroom floors and dumpsters</t>
+          <t>Trash cans, restroom floors and dumpsters (1:50). Sinks and food-contact surfaces: 50-200 ppm only (about 1 tsp per gallon), checked with test strips</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
